--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -40,7 +40,7 @@
     <t>index.report.json</t>
   </si>
   <si>
-    <t>["cards-category","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner"]</t>
+    <t>["cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner","cards-banner"]</t>
   </si>
   <si>
     <t>index</t>
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-08T04:10:47.224Z</t>
+    <t>2026-04-08T04:45:52.666Z</t>
   </si>
   <si>
     <t>Grocery Delivery Near You - Order Groceries Online | Albertsons</t>
